--- a/V9_W8_B32/data_instructions/VLIW_Excel/Unit17_ConvLast_ClobalAveragePool_FC.xlsx
+++ b/V9_W8_B32/data_instructions/VLIW_Excel/Unit17_ConvLast_ClobalAveragePool_FC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V7\data_instructions\VLIW_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V9_W8_B32\data_instructions\VLIW_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F23A422-E276-420D-B251-D1AB460780E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A37E35-4DFE-4179-BA55-CBE09B4785A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{92D39E35-E6AD-4D32-9F4F-66752069E36D}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{92D39E35-E6AD-4D32-9F4F-66752069E36D}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="74">
   <si>
     <t>OP_Code</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -330,6 +330,10 @@
   </si>
   <si>
     <t>960/4-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Requant_Sel[3]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -565,9 +569,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -583,13 +584,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1053,6 +1057,9 @@
       <c r="M5" s="8" t="s">
         <v>66</v>
       </c>
+      <c r="N5" s="7" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
@@ -1061,11 +1068,11 @@
       <c r="C7" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="19" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="17"/>
-      <c r="F7" s="20"/>
+      <c r="F7" s="19"/>
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
@@ -1096,9 +1103,9 @@
         <v>0</v>
       </c>
       <c r="C8" s="17"/>
-      <c r="D8" s="21"/>
+      <c r="D8" s="20"/>
       <c r="E8" s="17"/>
-      <c r="F8" s="21"/>
+      <c r="F8" s="20"/>
       <c r="G8" s="17"/>
       <c r="H8" s="17"/>
       <c r="I8" s="17"/>
@@ -1139,9 +1146,9 @@
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C9" s="17"/>
-      <c r="D9" s="21"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="17"/>
-      <c r="F9" s="21"/>
+      <c r="F9" s="20"/>
       <c r="G9" s="17"/>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
@@ -1163,9 +1170,9 @@
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C10" s="17"/>
-      <c r="D10" s="21"/>
+      <c r="D10" s="20"/>
       <c r="E10" s="17"/>
-      <c r="F10" s="21"/>
+      <c r="F10" s="20"/>
       <c r="G10" s="17"/>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
@@ -1194,9 +1201,9 @@
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C11" s="17"/>
-      <c r="D11" s="22"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="17"/>
-      <c r="F11" s="22"/>
+      <c r="F11" s="21"/>
       <c r="G11" s="17"/>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
@@ -1225,13 +1232,13 @@
       <c r="C12" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="23" t="s">
+      <c r="E12" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="22" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="17"/>
@@ -1264,9 +1271,9 @@
         <v>1</v>
       </c>
       <c r="C13" s="17"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="23"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="22"/>
       <c r="G13" s="17"/>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -1307,9 +1314,9 @@
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C14" s="17"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="23"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="22"/>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -1340,9 +1347,9 @@
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C15" s="17"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="23"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="22"/>
       <c r="G15" s="17"/>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -1371,9 +1378,9 @@
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C16" s="17"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="23"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="22"/>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -1402,16 +1409,16 @@
       <c r="C17" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="19" t="s">
+      <c r="D17" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="23" t="s">
+      <c r="F17" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="22" t="s">
         <v>26</v>
       </c>
       <c r="H17" s="17"/>
@@ -1443,10 +1450,10 @@
         <v>2</v>
       </c>
       <c r="C18" s="17"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="23"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="22"/>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
@@ -1486,10 +1493,10 @@
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C19" s="17"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="23"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="22"/>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
@@ -1519,10 +1526,10 @@
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C20" s="17"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="23"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="22"/>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
@@ -1550,10 +1557,10 @@
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C21" s="17"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="23"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="22"/>
       <c r="H21" s="17"/>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
@@ -1581,19 +1588,19 @@
       <c r="C22" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="23" t="s">
+      <c r="E22" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="22" t="s">
         <v>26</v>
       </c>
       <c r="I22" s="17"/>
@@ -1624,11 +1631,11 @@
         <v>3</v>
       </c>
       <c r="C23" s="17"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="23"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="22"/>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="L23" s="11" t="s">
@@ -1667,11 +1674,11 @@
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C24" s="17"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="23"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="22"/>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="L24" s="12" t="s">
@@ -1700,11 +1707,11 @@
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C25" s="17"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="23"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="22"/>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
       <c r="L25" s="14" t="s">
@@ -1731,11 +1738,11 @@
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C26" s="17"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="23"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="22"/>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
       <c r="L26" s="15" t="s">
@@ -1759,20 +1766,20 @@
       <c r="C27" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="19" t="s">
+      <c r="D27" s="19"/>
+      <c r="E27" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I27" s="23" t="s">
+      <c r="F27" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="22" t="s">
         <v>26</v>
       </c>
       <c r="J27" s="17"/>
@@ -1799,12 +1806,12 @@
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C28" s="17"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="23"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="22"/>
       <c r="J28" s="17"/>
       <c r="L28" s="11" t="s">
         <v>5</v>
@@ -1842,12 +1849,12 @@
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C29" s="17"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="23"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="22"/>
       <c r="J29" s="17"/>
       <c r="L29" s="12" t="s">
         <v>15</v>
@@ -1875,12 +1882,12 @@
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C30" s="17"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="23"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="22"/>
       <c r="J30" s="17"/>
       <c r="L30" s="14" t="s">
         <v>17</v>
@@ -1905,12 +1912,12 @@
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.45">
       <c r="C31" s="17"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="23"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="22"/>
       <c r="J31" s="17"/>
       <c r="L31" s="15" t="s">
         <v>23</v>
@@ -1931,20 +1938,20 @@
       <c r="C32" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="22" t="s">
         <v>26</v>
       </c>
       <c r="E32" s="17"/>
-      <c r="F32" s="19" t="s">
+      <c r="F32" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="G32" s="19" t="s">
+      <c r="G32" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="H32" s="19" t="s">
+      <c r="H32" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="I32" s="19" t="s">
+      <c r="I32" s="18" t="s">
         <v>33</v>
       </c>
       <c r="J32" s="17"/>
@@ -1971,12 +1978,12 @@
     </row>
     <row r="33" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C33" s="17"/>
-      <c r="D33" s="23"/>
+      <c r="D33" s="22"/>
       <c r="E33" s="17"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
       <c r="J33" s="17"/>
       <c r="L33" s="11" t="s">
         <v>5</v>
@@ -2014,12 +2021,12 @@
     </row>
     <row r="34" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C34" s="17"/>
-      <c r="D34" s="23"/>
+      <c r="D34" s="22"/>
       <c r="E34" s="17"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
       <c r="J34" s="17"/>
       <c r="L34" s="12" t="s">
         <v>15</v>
@@ -2047,12 +2054,12 @@
     </row>
     <row r="35" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C35" s="17"/>
-      <c r="D35" s="23"/>
+      <c r="D35" s="22"/>
       <c r="E35" s="17"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
       <c r="J35" s="17"/>
       <c r="L35" s="14" t="s">
         <v>17</v>
@@ -2077,12 +2084,12 @@
     </row>
     <row r="36" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C36" s="17"/>
-      <c r="D36" s="23"/>
+      <c r="D36" s="22"/>
       <c r="E36" s="17"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
       <c r="J36" s="17"/>
       <c r="L36" s="15" t="s">
         <v>23</v>
@@ -2107,7 +2114,7 @@
         <v>53</v>
       </c>
       <c r="E37" s="17"/>
-      <c r="F37" s="20"/>
+      <c r="F37" s="19"/>
       <c r="G37" s="17"/>
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
@@ -2137,7 +2144,7 @@
       <c r="C38" s="17"/>
       <c r="D38" s="25"/>
       <c r="E38" s="17"/>
-      <c r="F38" s="21"/>
+      <c r="F38" s="20"/>
       <c r="G38" s="17"/>
       <c r="H38" s="17"/>
       <c r="I38" s="17"/>
@@ -2180,7 +2187,7 @@
       <c r="C39" s="17"/>
       <c r="D39" s="25"/>
       <c r="E39" s="17"/>
-      <c r="F39" s="21"/>
+      <c r="F39" s="20"/>
       <c r="G39" s="17"/>
       <c r="H39" s="17"/>
       <c r="I39" s="17"/>
@@ -2205,7 +2212,7 @@
       <c r="C40" s="17"/>
       <c r="D40" s="25"/>
       <c r="E40" s="17"/>
-      <c r="F40" s="21"/>
+      <c r="F40" s="20"/>
       <c r="G40" s="17"/>
       <c r="H40" s="17"/>
       <c r="I40" s="17"/>
@@ -2235,7 +2242,7 @@
       <c r="C41" s="17"/>
       <c r="D41" s="25"/>
       <c r="E41" s="17"/>
-      <c r="F41" s="22"/>
+      <c r="F41" s="21"/>
       <c r="G41" s="17"/>
       <c r="H41" s="17"/>
       <c r="I41" s="17"/>
@@ -2259,15 +2266,15 @@
       <c r="C42" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="18" t="s">
         <v>33</v>
       </c>
       <c r="E42" s="17"/>
-      <c r="F42" s="20"/>
+      <c r="F42" s="19"/>
       <c r="G42" s="17"/>
       <c r="H42" s="17"/>
       <c r="I42" s="17"/>
-      <c r="J42" s="23" t="s">
+      <c r="J42" s="22" t="s">
         <v>26</v>
       </c>
       <c r="L42" s="9" t="s">
@@ -2292,13 +2299,13 @@
     </row>
     <row r="43" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C43" s="17"/>
-      <c r="D43" s="19"/>
+      <c r="D43" s="18"/>
       <c r="E43" s="17"/>
-      <c r="F43" s="21"/>
+      <c r="F43" s="20"/>
       <c r="G43" s="17"/>
       <c r="H43" s="17"/>
       <c r="I43" s="17"/>
-      <c r="J43" s="23"/>
+      <c r="J43" s="22"/>
       <c r="L43" s="11" t="s">
         <v>5</v>
       </c>
@@ -2335,13 +2342,13 @@
     </row>
     <row r="44" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C44" s="17"/>
-      <c r="D44" s="19"/>
+      <c r="D44" s="18"/>
       <c r="E44" s="17"/>
-      <c r="F44" s="21"/>
+      <c r="F44" s="20"/>
       <c r="G44" s="17"/>
       <c r="H44" s="17"/>
       <c r="I44" s="17"/>
-      <c r="J44" s="23"/>
+      <c r="J44" s="22"/>
       <c r="L44" s="12" t="s">
         <v>15</v>
       </c>
@@ -2368,13 +2375,13 @@
     </row>
     <row r="45" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C45" s="17"/>
-      <c r="D45" s="19"/>
+      <c r="D45" s="18"/>
       <c r="E45" s="17"/>
-      <c r="F45" s="21"/>
+      <c r="F45" s="20"/>
       <c r="G45" s="17"/>
       <c r="H45" s="17"/>
       <c r="I45" s="17"/>
-      <c r="J45" s="23"/>
+      <c r="J45" s="22"/>
       <c r="L45" s="14" t="s">
         <v>17</v>
       </c>
@@ -2398,13 +2405,13 @@
     </row>
     <row r="46" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C46" s="17"/>
-      <c r="D46" s="19"/>
+      <c r="D46" s="18"/>
       <c r="E46" s="17"/>
-      <c r="F46" s="22"/>
+      <c r="F46" s="21"/>
       <c r="G46" s="17"/>
       <c r="H46" s="17"/>
       <c r="I46" s="17"/>
-      <c r="J46" s="23"/>
+      <c r="J46" s="22"/>
       <c r="L46" s="15" t="s">
         <v>23</v>
       </c>
@@ -2424,13 +2431,13 @@
       <c r="C47" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D47" s="19"/>
+      <c r="D47" s="18"/>
       <c r="E47" s="17"/>
-      <c r="F47" s="20"/>
+      <c r="F47" s="19"/>
       <c r="G47" s="17"/>
       <c r="H47" s="17"/>
       <c r="I47" s="17"/>
-      <c r="J47" s="18" t="s">
+      <c r="J47" s="26" t="s">
         <v>33</v>
       </c>
       <c r="L47" s="9" t="s">
@@ -2456,13 +2463,13 @@
     </row>
     <row r="48" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C48" s="17"/>
-      <c r="D48" s="19"/>
+      <c r="D48" s="18"/>
       <c r="E48" s="17"/>
-      <c r="F48" s="21"/>
+      <c r="F48" s="20"/>
       <c r="G48" s="17"/>
       <c r="H48" s="17"/>
       <c r="I48" s="17"/>
-      <c r="J48" s="18"/>
+      <c r="J48" s="26"/>
       <c r="L48" s="11" t="s">
         <v>5</v>
       </c>
@@ -2499,13 +2506,13 @@
     </row>
     <row r="49" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C49" s="17"/>
-      <c r="D49" s="19"/>
+      <c r="D49" s="18"/>
       <c r="E49" s="17"/>
-      <c r="F49" s="21"/>
+      <c r="F49" s="20"/>
       <c r="G49" s="17"/>
       <c r="H49" s="17"/>
       <c r="I49" s="17"/>
-      <c r="J49" s="18"/>
+      <c r="J49" s="26"/>
       <c r="L49" s="12" t="s">
         <v>15</v>
       </c>
@@ -2524,13 +2531,13 @@
     </row>
     <row r="50" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C50" s="17"/>
-      <c r="D50" s="19"/>
+      <c r="D50" s="18"/>
       <c r="E50" s="17"/>
-      <c r="F50" s="21"/>
+      <c r="F50" s="20"/>
       <c r="G50" s="17"/>
       <c r="H50" s="17"/>
       <c r="I50" s="17"/>
-      <c r="J50" s="18"/>
+      <c r="J50" s="26"/>
       <c r="L50" s="14" t="s">
         <v>17</v>
       </c>
@@ -2554,13 +2561,13 @@
     </row>
     <row r="51" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C51" s="17"/>
-      <c r="D51" s="19"/>
+      <c r="D51" s="18"/>
       <c r="E51" s="17"/>
-      <c r="F51" s="22"/>
+      <c r="F51" s="21"/>
       <c r="G51" s="17"/>
       <c r="H51" s="17"/>
       <c r="I51" s="17"/>
-      <c r="J51" s="18"/>
+      <c r="J51" s="26"/>
       <c r="L51" s="15" t="s">
         <v>23</v>
       </c>
@@ -2578,6 +2585,62 @@
     </row>
   </sheetData>
   <mergeCells count="72">
+    <mergeCell ref="I47:I51"/>
+    <mergeCell ref="J47:J51"/>
+    <mergeCell ref="C47:C51"/>
+    <mergeCell ref="D47:D51"/>
+    <mergeCell ref="E47:E51"/>
+    <mergeCell ref="F47:F51"/>
+    <mergeCell ref="G47:G51"/>
+    <mergeCell ref="H47:H51"/>
+    <mergeCell ref="I37:I41"/>
+    <mergeCell ref="J37:J41"/>
+    <mergeCell ref="C42:C46"/>
+    <mergeCell ref="D42:D46"/>
+    <mergeCell ref="E42:E46"/>
+    <mergeCell ref="F42:F46"/>
+    <mergeCell ref="G42:G46"/>
+    <mergeCell ref="H42:H46"/>
+    <mergeCell ref="I42:I46"/>
+    <mergeCell ref="J42:J46"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="D37:D41"/>
+    <mergeCell ref="E37:E41"/>
+    <mergeCell ref="F37:F41"/>
+    <mergeCell ref="G37:G41"/>
+    <mergeCell ref="H37:H41"/>
+    <mergeCell ref="I27:I31"/>
+    <mergeCell ref="J27:J31"/>
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="D32:D36"/>
+    <mergeCell ref="E32:E36"/>
+    <mergeCell ref="F32:F36"/>
+    <mergeCell ref="G32:G36"/>
+    <mergeCell ref="H32:H36"/>
+    <mergeCell ref="I32:I36"/>
+    <mergeCell ref="J32:J36"/>
+    <mergeCell ref="C27:C31"/>
+    <mergeCell ref="D27:D31"/>
+    <mergeCell ref="E27:E31"/>
+    <mergeCell ref="F27:F31"/>
+    <mergeCell ref="G27:G31"/>
+    <mergeCell ref="H27:H31"/>
+    <mergeCell ref="I17:I21"/>
+    <mergeCell ref="J17:J21"/>
+    <mergeCell ref="C22:C26"/>
+    <mergeCell ref="D22:D26"/>
+    <mergeCell ref="E22:E26"/>
+    <mergeCell ref="F22:F26"/>
+    <mergeCell ref="G22:G26"/>
+    <mergeCell ref="H22:H26"/>
+    <mergeCell ref="I22:I26"/>
+    <mergeCell ref="J22:J26"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="E17:E21"/>
+    <mergeCell ref="F17:F21"/>
+    <mergeCell ref="G17:G21"/>
+    <mergeCell ref="H17:H21"/>
     <mergeCell ref="I7:I11"/>
     <mergeCell ref="J7:J11"/>
     <mergeCell ref="C12:C16"/>
@@ -2594,62 +2657,6 @@
     <mergeCell ref="F7:F11"/>
     <mergeCell ref="G7:G11"/>
     <mergeCell ref="H7:H11"/>
-    <mergeCell ref="I17:I21"/>
-    <mergeCell ref="J17:J21"/>
-    <mergeCell ref="C22:C26"/>
-    <mergeCell ref="D22:D26"/>
-    <mergeCell ref="E22:E26"/>
-    <mergeCell ref="F22:F26"/>
-    <mergeCell ref="G22:G26"/>
-    <mergeCell ref="H22:H26"/>
-    <mergeCell ref="I22:I26"/>
-    <mergeCell ref="J22:J26"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="E17:E21"/>
-    <mergeCell ref="F17:F21"/>
-    <mergeCell ref="G17:G21"/>
-    <mergeCell ref="H17:H21"/>
-    <mergeCell ref="I27:I31"/>
-    <mergeCell ref="J27:J31"/>
-    <mergeCell ref="C32:C36"/>
-    <mergeCell ref="D32:D36"/>
-    <mergeCell ref="E32:E36"/>
-    <mergeCell ref="F32:F36"/>
-    <mergeCell ref="G32:G36"/>
-    <mergeCell ref="H32:H36"/>
-    <mergeCell ref="I32:I36"/>
-    <mergeCell ref="J32:J36"/>
-    <mergeCell ref="C27:C31"/>
-    <mergeCell ref="D27:D31"/>
-    <mergeCell ref="E27:E31"/>
-    <mergeCell ref="F27:F31"/>
-    <mergeCell ref="G27:G31"/>
-    <mergeCell ref="H27:H31"/>
-    <mergeCell ref="I37:I41"/>
-    <mergeCell ref="J37:J41"/>
-    <mergeCell ref="C42:C46"/>
-    <mergeCell ref="D42:D46"/>
-    <mergeCell ref="E42:E46"/>
-    <mergeCell ref="F42:F46"/>
-    <mergeCell ref="G42:G46"/>
-    <mergeCell ref="H42:H46"/>
-    <mergeCell ref="I42:I46"/>
-    <mergeCell ref="J42:J46"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="D37:D41"/>
-    <mergeCell ref="E37:E41"/>
-    <mergeCell ref="F37:F41"/>
-    <mergeCell ref="G37:G41"/>
-    <mergeCell ref="H37:H41"/>
-    <mergeCell ref="I47:I51"/>
-    <mergeCell ref="J47:J51"/>
-    <mergeCell ref="C47:C51"/>
-    <mergeCell ref="D47:D51"/>
-    <mergeCell ref="E47:E51"/>
-    <mergeCell ref="F47:F51"/>
-    <mergeCell ref="G47:G51"/>
-    <mergeCell ref="H47:H51"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
